--- a/wanlong_service_retail_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/wanlong_service_retail_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -743,6 +743,11 @@
           <t>正/闭</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>七色米订单号</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -868,6 +873,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -993,6 +999,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1118,6 +1125,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1263,6 +1271,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1428,6 +1437,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1593,6 +1603,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>XSD20251013002I</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1741,6 +1756,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1889,6 +1905,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2062,6 +2079,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>XSD20251201001A</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2235,6 +2257,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>XSD20251201002A</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2408,6 +2435,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>XSD20251205002A</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2581,6 +2613,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>XSD20251206007A</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2754,6 +2791,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>XSD20251206005A</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2927,6 +2969,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>XSD20251215004A</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3100,6 +3147,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>XSD20251224009A</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3263,6 +3315,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>XSD20251229000A</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3436,6 +3493,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>XSD20260101025A</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3609,6 +3671,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>XSD20260101024A</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3782,6 +3849,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>XSD20260328001A</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3955,6 +4027,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>XSD20260125003A</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4118,6 +4195,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>XSD20260201001A</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4291,6 +4373,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>XSD20260204000A</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4464,6 +4551,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>XSD20260210005A</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4637,6 +4729,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>XSD20260210004A</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4800,6 +4897,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>XSD20260212009A</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4973,6 +5075,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>XSD20260218002A</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5146,6 +5253,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>XSD20260223003A</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5319,6 +5431,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>XSD20260309002A</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5492,6 +5609,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>XSD20260312000A</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5665,6 +5787,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5836,6 +5959,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>XSD20260328000A</t>
         </is>
       </c>
     </row>
@@ -5931,7 +6059,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -5971,7 +6098,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -6319,7 +6445,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>2088002091495981</t>
@@ -6535,7 +6660,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>2088212898624044</t>
@@ -6707,7 +6831,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>2088002720576405</t>
@@ -7074,7 +7197,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>WF_LS_251013_00001_ZF_01</t>
@@ -7110,7 +7232,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>WF_LS_251013_00002_ZF_01</t>
@@ -7426,7 +7547,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>WF_LS_251227_00001_ZF_02</t>
@@ -7622,7 +7742,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>WF_LS_260131_00001_ZF_01</t>
@@ -7778,7 +7897,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>WF_LS_260212_00001_ZF_01</t>

--- a/wanlong_service_retail_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/wanlong_service_retail_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="年度零售" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度零售" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度零售明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -34,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,13 +66,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -873,7 +883,6 @@
           <t>关闭</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -999,7 +1008,6 @@
           <t>关闭</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1125,7 +1133,6 @@
           <t>关闭</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1271,7 +1278,6 @@
           <t>关闭</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1437,7 +1443,6 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1756,7 +1761,6 @@
           <t>关闭</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1905,7 +1909,6 @@
           <t>关闭</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5787,7 +5790,6 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8164,4 +8166,5205 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BK24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="30" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="30" customWidth="1" min="47" max="47"/>
+    <col width="6" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="7" customWidth="1" min="51" max="51"/>
+    <col width="17" customWidth="1" min="52" max="52"/>
+    <col width="16" customWidth="1" min="53" max="53"/>
+    <col width="36" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="6" customWidth="1" min="56" max="56"/>
+    <col width="6" customWidth="1" min="57" max="57"/>
+    <col width="6" customWidth="1" min="58" max="58"/>
+    <col width="8" customWidth="1" min="59" max="59"/>
+    <col width="7" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="8" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>业务</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>财年</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>营/非</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>财年序号</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>运营日序号</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>日序号</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>创建日期</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>支付次数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>支付合计</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>退款次数</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>退款合计</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>订单结余</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>最后退款日期</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>最后退款时间</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>【支付1】日期</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>【支付1】时间</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>【支付1】金额</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>【支付1】支付方式</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>【支付1】支付账号</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>零售件数</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>销售额合计</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>招待件数</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>减免合计</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>隐藏订单</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>应分账金额</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>实分账金额</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>待分账金额</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>业务</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>顾客openid</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>收款方式</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>支付账号</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>业务日期</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>业务时间</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>结算日期</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>结算时间</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>支付总金额</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>退款总金额</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>订单结余</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>店员姓名</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>店员openid</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>临时订单</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>正/闭</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>七色米订单号</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>商品分类</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>属性</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>折扣</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>折后单价</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>总额</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Σ明细总额−订单结余</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12:10:34</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>12:11:07</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>郝</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>13903518351</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>oHdTn5f-A5m8LR3Et3Nl6ssu_C-c</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>WF_LS_251201_00001</t>
+        </is>
+      </c>
+      <c r="AM2" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>12:10:34</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>郝</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>XSD20251201001A</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI2" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ2" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12:17:37</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>12:18:12</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>小付姐</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>13803340368</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>oHdTn5TIVAyw8SXXr7W5Sq53wy7E</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>WF_LS_251201_00002</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="n">
+        <v>45992</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>12:17:37</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>小付姐</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>XSD20251201002A</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG3" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI3" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ3" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>45996</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17:34:12</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>800</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>800</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>45996</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>17:34:33</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>800</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>裴</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>13931032229</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>oHdTn5bHJxQHQQRfLbi9hd6CjXHA</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>WF_LS_251205_00001</t>
+        </is>
+      </c>
+      <c r="AM4" s="6" t="n">
+        <v>45996</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>17:34:12</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>800</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>800</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>裴</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>XSD20251205002A</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>SP20251127016I</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>机打蜡季卡 25-26</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>80</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>45997</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10:36:42</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>45997</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10:37:08</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>郭</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>18801419929</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>oHdTn5YxP_8vGXoI8WvzcWiBVzkw</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>WF_LS_251206_00001</t>
+        </is>
+      </c>
+      <c r="AM5" s="6" t="n">
+        <v>45997</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>10:36:42</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>郭</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>XSD20251206007A</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG5" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI5" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ5" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>45997</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11:56:43</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>45997</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>11:57:03</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>13632976861</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>oHdTn5XCdSINaIyM0w55LVMnpk2A</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>WF_LS_251206_00002</t>
+        </is>
+      </c>
+      <c r="AM6" s="6" t="n">
+        <v>45997</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>11:56:43</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>XSD20251206005A</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG6" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="BI6" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ6" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>46006</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13:48:54</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>46006</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>13:49:22</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>朱</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>13901163883</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>oHdTn5dxgDDmZcdG5HZW_jzpu3I0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>WF_LS_251215_00001</t>
+        </is>
+      </c>
+      <c r="AM7" s="6" t="n">
+        <v>46006</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>13:48:54</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>朱</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>XSD20251215004A</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG7" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI7" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ7" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>46010</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15:35:54</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>46010</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>15:36:14</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>崔</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>13501000728</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>oHdTn5VCyUBcR7qlwxeoD8cqr0bw</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>WF_LS_251219_00001</t>
+        </is>
+      </c>
+      <c r="AM8" s="6" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>15:35:54</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>崔</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>XSD20251224009A</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG8" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI8" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ8" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>46018</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14:28:34</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>46018</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>14:29:00</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>13910020167</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>oHdTn5WvqfubAgLl--192O-CRFrs</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>WF_LS_251227_00001</t>
+        </is>
+      </c>
+      <c r="AM9" s="6" t="n">
+        <v>46018</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>14:28:34</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>XSD20251229000A</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG9" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI9" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ9" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12:24:29</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>46023</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>12:24:51</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>13811050876</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>oHdTn5WZBbk27VZHokdmv3D6eDZw</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>WF_LS_260101_00001</t>
+        </is>
+      </c>
+      <c r="AM10" s="6" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>12:24:29</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>XSD20260101025A</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG10" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="BI10" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ10" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>73</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15:48:09</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>46023</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>15:48:40</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>尤</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>13916963689</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>oHdTn5d6aVFb3EApJGzpvFBq5VVI</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>WF_LS_260101_00002</t>
+        </is>
+      </c>
+      <c r="AM11" s="6" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>15:48:09</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>尤</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>XSD20260101024A</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG11" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="BI11" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ11" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>46024</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15:33:55</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>46024</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>15:34:13</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>赵</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>13910998233</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>oHdTn5a3n4rPvIEN9yz9_UOeIIGw</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>WF_LS_260102_00001</t>
+        </is>
+      </c>
+      <c r="AM12" s="6" t="n">
+        <v>46024</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>15:33:55</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>赵</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>XSD20260328001A</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG12" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="BI12" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ12" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>97</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>46047</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>11:19:21</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>46047</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>11:19:44</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>芮</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>18601188863</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>oHdTn5WeZgUvaJ09fV6X7ZlbvDLc</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>WF_LS_260125_00001</t>
+        </is>
+      </c>
+      <c r="AM13" s="6" t="n">
+        <v>46047</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>11:19:21</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>芮</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>XSD20260125003A</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG13" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI13" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ13" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>46053</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16:20:29</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>46053</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>16:21:03</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>李</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>17717090753</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>oHdTn5TpAh0qsELkVF24JkhmrNE8</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>WF_LS_260131_00001</t>
+        </is>
+      </c>
+      <c r="AM14" s="6" t="n">
+        <v>46053</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>16:20:29</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>李</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>XSD20260201001A</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG14" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI14" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ14" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>107</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>09:34:00</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>46057</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>09:34:29</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>13686463740</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>oHdTn5Uvz5w234WZXozyAizpaKRo</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>WF_LS_260204_00001</t>
+        </is>
+      </c>
+      <c r="AM15" s="6" t="n">
+        <v>46057</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>09:34:00</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>XSD20260204000A</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG15" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ15" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>110</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>46060</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14:31:04</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>46060</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>14:31:32</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>仲</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>13073206313</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>oHdTn5RiZdGLLHI_V0kQUO-pyWro</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>WF_LS_260207_00001</t>
+        </is>
+      </c>
+      <c r="AM16" s="6" t="n">
+        <v>46060</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>14:31:04</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>仲</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>XSD20260210005A</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG16" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI16" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ16" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>113</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14:10:16</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>14:10:50</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>13811850850</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>oHdTn5aaiPGlf-IE3szAnY6ouc-c</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>WF_LS_260210_00001</t>
+        </is>
+      </c>
+      <c r="AM17" s="6" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>14:10:16</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>XSD20260210004A</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG17" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI17" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ17" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>115</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>46065</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13:52:51</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>46065</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>13:53:04</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>何</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>18420021917</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>oHdTn5cQRZgpc0Ccd93JzhQxhyYY</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>支付宝</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>WF_LS_260212_00001</t>
+        </is>
+      </c>
+      <c r="AM18" s="6" t="n">
+        <v>46065</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>13:52:51</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>何</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>XSD20260212009A</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>SP20251127009I</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>单项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG18" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI18" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="BJ18" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="BK18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>121</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>46071</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13:16:18</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>46071</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>13:16:42</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>邢</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>13911154110</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>oHdTn5SBvqambSYi1rqgUszaTtMs</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>WF_LS_260218_00001</t>
+        </is>
+      </c>
+      <c r="AM19" s="6" t="n">
+        <v>46071</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>13:16:18</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>邢</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>XSD20260218002A</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG19" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI19" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ19" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>126</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>46076</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12:43:51</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>46076</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>12:44:15</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>洋</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>13681116182</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>oHdTn5Y1JItXiGp-QeO2v7Mnil1U</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>WF_LS_260223_00001</t>
+        </is>
+      </c>
+      <c r="AM20" s="6" t="n">
+        <v>46076</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>12:43:51</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>洋</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>XSD20260223003A</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG20" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI20" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BJ20" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BK20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>137</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>46087</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11:38:21</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>46087</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>11:38:48</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>冯</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>18611388417</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>oHdTn5SKu4a3Gu5ipu7Fh6v7IW0Q</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>WF_LS_260306_00001</t>
+        </is>
+      </c>
+      <c r="AM21" s="6" t="n">
+        <v>46087</v>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>11:38:21</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>冯</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>XSD20260309002A</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG21" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="BI21" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BJ21" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="BK21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>143</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>46093</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12:42:44</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>46093</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>12:44:42</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>伍</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>18688803881</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>oHdTn5TvyXISKYYXzaJX2WKvqDRw</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>WF_LS_260312_00001</t>
+        </is>
+      </c>
+      <c r="AM22" s="6" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>12:42:44</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>伍</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>XSD20260312000A</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>SP20251127008I</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>双项养护10次卡</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>默认分类</t>
+        </is>
+      </c>
+      <c r="BF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG22" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="BI22" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ22" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>46096</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>15:53:27</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="5" t="n">
+        <v>46096</v>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>15:53:50</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="4" t="n"/>
+      <c r="AB23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF23" s="4" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG23" s="4" t="inlineStr">
+        <is>
+          <t>杨</t>
+        </is>
+      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
+          <t>18810482322</t>
+        </is>
+      </c>
+      <c r="AI23" s="4" t="inlineStr">
+        <is>
+          <t>oHdTn5SJpEiRoOoUIudwrmFCOL2c</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK23" s="4" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL23" s="4" t="inlineStr">
+        <is>
+          <t>WF_LS_260315_00001</t>
+        </is>
+      </c>
+      <c r="AM23" s="5" t="n">
+        <v>46096</v>
+      </c>
+      <c r="AN23" s="4" t="inlineStr">
+        <is>
+          <t>15:53:27</t>
+        </is>
+      </c>
+      <c r="AO23" s="4" t="n"/>
+      <c r="AP23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AR23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AT23" s="4" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU23" s="4" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AV23" s="4" t="n"/>
+      <c r="AW23" s="4" t="n"/>
+      <c r="AX23" s="4" t="inlineStr">
+        <is>
+          <t>杨</t>
+        </is>
+      </c>
+      <c r="AY23" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ23" s="4" t="n"/>
+      <c r="BA23" s="4" t="n"/>
+      <c r="BB23" s="4" t="n"/>
+      <c r="BC23" s="4" t="n"/>
+      <c r="BD23" s="4" t="n"/>
+      <c r="BE23" s="4" t="n"/>
+      <c r="BF23" s="4" t="n"/>
+      <c r="BG23" s="4" t="n"/>
+      <c r="BH23" s="4" t="n"/>
+      <c r="BI23" s="4" t="n"/>
+      <c r="BJ23" s="4" t="n"/>
+      <c r="BK23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>159</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13:28:16</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>319</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>319</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>13:28:36</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>319</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>319</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>万龙服务中心</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>18612325829</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>oHdTn5TiULTGJ-r-Ph5k93O-lqfs</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>1636404775</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>WF_LS_260328_00001</t>
+        </is>
+      </c>
+      <c r="AM24" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>13:28:16</t>
+        </is>
+      </c>
+      <c r="AQ24" t="n">
+        <v>319</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>319</v>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>XSD20260328000A</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>SP20251124004</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>Gallium雪蜡 SX0015液体蜡套装 G220ml+除蜡剂300ml 全雪温</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>Gallium</t>
+        </is>
+      </c>
+      <c r="BF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG24" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>319</v>
+      </c>
+      <c r="BJ24" s="3" t="n">
+        <v>319</v>
+      </c>
+      <c r="BK24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>